--- a/docs/data/jp/xlsx/6663.xlsx
+++ b/docs/data/jp/xlsx/6663.xlsx
@@ -1152,7 +1152,7 @@
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>전자기판 사업</t>
         </is>
       </c>
       <c r="B7" s="10" t="n"/>
@@ -1430,7 +1430,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>테스트시스템 사업</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -1708,7 +1708,7 @@
     <row r="13">
       <c r="A13" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>경면연마기 사업</t>
         </is>
       </c>
       <c r="B13" s="10" t="n"/>
@@ -1986,7 +1986,7 @@
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>부문</t>
+          <t>산업기계시스템 사업</t>
         </is>
       </c>
       <c r="B16" s="10" t="n"/>
@@ -7180,7 +7180,7 @@
     <row r="100">
       <c r="A100" s="18" t="inlineStr">
         <is>
-          <t>Loss On Transfer Of Receivables NOE</t>
+          <t>채권매각손실</t>
         </is>
       </c>
       <c r="C100" s="20" t="n">
@@ -7232,7 +7232,7 @@
     <row r="101">
       <c r="A101" s="18" t="inlineStr">
         <is>
-          <t>Amortization Of Restricted Stock Compensation NOE</t>
+          <t>양도제한조건부 주식보상 상각</t>
         </is>
       </c>
       <c r="S101" s="20" t="n">
@@ -7380,7 +7380,7 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>Ordinary Income</t>
+          <t>경상이익(손실)</t>
         </is>
       </c>
       <c r="C105" s="12" t="n">
@@ -7524,7 +7524,7 @@
     <row r="108">
       <c r="A108" s="18" t="inlineStr">
         <is>
-          <t>Gain On Capital Reduction With Compensation Of Subsidiaries And Associates EI</t>
+          <t>관계회사 유상감자 환급차익</t>
         </is>
       </c>
       <c r="J108" s="20" t="n">
@@ -7712,7 +7712,7 @@
     <row r="113">
       <c r="A113" s="18" t="inlineStr">
         <is>
-          <t>Early Extra Retirement Payments EL</t>
+          <t>조기 특별퇴직금</t>
         </is>
       </c>
       <c r="E113" s="20" t="n">
@@ -7795,7 +7795,7 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>Income Before Income Taxes</t>
+          <t>법인세차감전 중간순이익(손실)</t>
         </is>
       </c>
       <c r="C115" s="12" t="n">
@@ -7899,7 +7899,7 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>Profit Loss</t>
+          <t>중간순이익(손실)</t>
         </is>
       </c>
       <c r="C117" s="12" t="n">
@@ -8003,7 +8003,7 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>Profit Loss Attributable To Owners Of Parent</t>
+          <t>지배주주 귀속 중간순이익(손실)</t>
         </is>
       </c>
       <c r="C119" s="12" t="n">
@@ -8241,7 +8241,7 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>Profit Loss</t>
+          <t>중간순이익(손실)</t>
         </is>
       </c>
       <c r="C123" s="12" t="n">
@@ -8791,7 +8791,7 @@
     <row r="133">
       <c r="A133" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>전자기판 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C133" s="20" t="n">
@@ -8834,7 +8834,7 @@
     <row r="134">
       <c r="A134" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>테스트시스템 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C134" s="20" t="n">
@@ -8877,7 +8877,7 @@
     <row r="135">
       <c r="A135" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>경면연마기 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C135" s="20" t="n">
@@ -8920,7 +8920,7 @@
     <row r="136">
       <c r="A136" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>산업기계시스템 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C136" s="20" t="n">
@@ -9092,7 +9092,7 @@
     <row r="140">
       <c r="A140" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>전자기판 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C140" s="20" t="n">
@@ -9135,7 +9135,7 @@
     <row r="141">
       <c r="A141" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>테스트시스템 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C141" s="20" t="n">
@@ -9178,7 +9178,7 @@
     <row r="142">
       <c r="A142" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>경면연마기 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C142" s="20" t="n">
@@ -9221,7 +9221,7 @@
     <row r="143">
       <c r="A143" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 간 내부매출·대체</t>
+          <t>산업기계시스템 사업 · 부문 간 내부매출·대체</t>
         </is>
       </c>
       <c r="C143" s="20" t="n">
@@ -9393,7 +9393,7 @@
     <row r="147">
       <c r="A147" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>전자기판 사업 · 계</t>
         </is>
       </c>
       <c r="C147" s="20" t="n">
@@ -9436,7 +9436,7 @@
     <row r="148">
       <c r="A148" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>테스트시스템 사업 · 계</t>
         </is>
       </c>
       <c r="C148" s="20" t="n">
@@ -9479,7 +9479,7 @@
     <row r="149">
       <c r="A149" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>경면연마기 사업 · 계</t>
         </is>
       </c>
       <c r="C149" s="20" t="n">
@@ -9522,7 +9522,7 @@
     <row r="150">
       <c r="A150" s="18" t="inlineStr">
         <is>
-          <t>부문 · 계</t>
+          <t>산업기계시스템 사업 · 계</t>
         </is>
       </c>
       <c r="C150" s="20" t="n">
@@ -9694,7 +9694,7 @@
     <row r="154">
       <c r="A154" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익(손실)</t>
+          <t>전자기판 사업 · 부문 이익(손실)</t>
         </is>
       </c>
       <c r="C154" s="20" t="n">
@@ -9737,7 +9737,7 @@
     <row r="155">
       <c r="A155" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익(손실)</t>
+          <t>테스트시스템 사업 · 부문 이익(손실)</t>
         </is>
       </c>
       <c r="C155" s="20" t="n">
@@ -9780,7 +9780,7 @@
     <row r="156">
       <c r="A156" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익(손실)</t>
+          <t>경면연마기 사업 · 부문 이익(손실)</t>
         </is>
       </c>
       <c r="C156" s="20" t="n">
@@ -9823,7 +9823,7 @@
     <row r="157">
       <c r="A157" s="18" t="inlineStr">
         <is>
-          <t>부문 · 부문 이익(손실)</t>
+          <t>산업기계시스템 사업 · 부문 이익(손실)</t>
         </is>
       </c>
       <c r="C157" s="20" t="n">
@@ -10181,7 +10181,7 @@
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>Income Before Income Taxes</t>
+          <t>법인세차감전 중간순이익(손실)</t>
         </is>
       </c>
       <c r="D164" s="12" t="n">
@@ -10914,7 +10914,7 @@
     <row r="180">
       <c r="A180" s="18" t="inlineStr">
         <is>
-          <t>Extra Payments For Early Retirements Ope CF</t>
+          <t>조기 특별퇴직금</t>
         </is>
       </c>
       <c r="D180" s="20" t="n">
@@ -11327,7 +11327,7 @@
     <row r="188">
       <c r="A188" s="18" t="inlineStr">
         <is>
-          <t>Extra Payments For Early Retirements Paid Ope CF</t>
+          <t>조기 특별퇴직금 지급액</t>
         </is>
       </c>
       <c r="H188" s="20" t="n">
@@ -11824,7 +11824,7 @@
     <row r="199">
       <c r="A199" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Liquidation Of Investment Securities Inv CF</t>
+          <t>투자유가증권 청산 수입</t>
         </is>
       </c>
       <c r="S199" s="20" t="n">
@@ -12312,7 +12312,7 @@
     <row r="210">
       <c r="A210" s="18" t="inlineStr">
         <is>
-          <t>Payments For Long Term Accounts Payable Other Fin CF</t>
+          <t>장기 미지급금 상환 지출</t>
         </is>
       </c>
       <c r="D210" s="20" t="n">
